--- a/file/table/TSIG_WindSpeedDirectionSample.xlsx
+++ b/file/table/TSIG_WindSpeedDirectionSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40392A84-353E-4C92-B925-4D8D18BD9A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FEA018-2E37-4173-BCF5-2F6B4A0E2D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{72E4CBD1-0E4B-4C3C-BF1D-B2D91BD85BCD}"/>
+    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" xr2:uid="{72E4CBD1-0E4B-4C3C-BF1D-B2D91BD85BCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Wind" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Wind speed and wind direction calculation from u10 and v10 vector fields</t>
   </si>
@@ -47,10 +47,28 @@
     <t>v10 (m/s)</t>
   </si>
   <si>
-    <t>vel (m/s)</t>
-  </si>
-  <si>
     <t>Dir (°)</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>import math as math</t>
+  </si>
+  <si>
+    <t>Vel (m/s)</t>
+  </si>
+  <si>
+    <t>east</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
+    <t>vel = (u10**2 + v10**2)**0.5</t>
+  </si>
+  <si>
+    <t>dir = (math.atan2(v10, u10) * 180 / math.pi) % 360</t>
   </si>
 </sst>
 </file>
@@ -436,50 +454,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51C11F4-B029-46A6-B1B9-D3E8BF3A8046}">
-  <dimension ref="B2:C6"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:D11"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="2.796875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+        <v>-5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <f>(C3^2+C4^2)^0.5</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
+        <v>9.4339811320566032</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <f>MOD(ATAN2(C3,C4)*180/PI(),360)</f>
-        <v>126.86989764584402</v>
+        <v>122.0053832080835</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
